--- a/logs/codenames_collaborative/o1-mini_wo_sys_mes/accuracy_results_o1-mini_wo_sys_mes.xlsx
+++ b/logs/codenames_collaborative/o1-mini_wo_sys_mes/accuracy_results_o1-mini_wo_sys_mes.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -918,7 +918,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -964,7 +964,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -987,7 +987,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1010,7 +1010,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1033,7 +1033,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1056,7 +1056,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1148,7 +1148,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1286,7 +1286,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1332,7 +1332,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1355,7 +1355,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1401,7 +1401,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1493,7 +1493,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1562,7 +1562,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1608,7 +1608,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-bpp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1633,7 +1633,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1656,7 +1656,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1702,7 +1702,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1748,7 +1748,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1794,7 +1794,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1817,7 +1817,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1886,7 +1886,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1909,7 +1909,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1932,7 +1932,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1955,7 +1955,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1978,7 +1978,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2001,7 +2001,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2024,7 +2024,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2047,7 +2047,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2070,7 +2070,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2093,7 +2093,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2162,7 +2162,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2185,7 +2185,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2208,7 +2208,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2231,7 +2231,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2277,7 +2277,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2300,7 +2300,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2346,7 +2346,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2392,7 +2392,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2415,7 +2415,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2438,7 +2438,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2461,7 +2461,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2484,7 +2484,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2530,7 +2530,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2553,7 +2553,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2576,7 +2576,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2599,7 +2599,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2622,7 +2622,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2668,7 +2668,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2691,7 +2691,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2714,7 +2714,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2737,7 +2737,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2760,7 +2760,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2783,7 +2783,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-spp_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2808,7 +2808,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2854,7 +2854,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2877,7 +2877,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2900,7 +2900,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2923,7 +2923,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2946,7 +2946,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2969,7 +2969,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3015,7 +3015,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3038,7 +3038,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3084,7 +3084,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3107,7 +3107,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3130,7 +3130,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3176,7 +3176,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3199,7 +3199,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3245,7 +3245,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3268,7 +3268,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3291,7 +3291,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3314,7 +3314,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3360,7 +3360,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3383,7 +3383,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3406,7 +3406,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3429,7 +3429,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3475,7 +3475,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3498,7 +3498,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3567,7 +3567,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3590,7 +3590,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3613,7 +3613,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3659,7 +3659,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3682,7 +3682,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3705,7 +3705,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3728,7 +3728,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3751,7 +3751,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3774,7 +3774,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3797,7 +3797,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3820,7 +3820,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3843,7 +3843,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3866,7 +3866,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3889,7 +3889,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3912,7 +3912,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3935,7 +3935,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50__wo_sys.jsonl</t>
+          <t>codenames_50.jsonl__method-standard_model-o1-mini_temp-_temp-1.0_topp-_topp-1.0_start0-end50_run01__wo_sys.jsonl</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
